--- a/output/graficos_nacionales/plot_nacional_e_basneta_a_2018.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_basneta_a_2018.xlsx
@@ -85,12 +85,6 @@
     <t xml:space="preserve">O Higgins</t>
   </si>
   <si>
-    <t xml:space="preserve">11201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aysén</t>
-  </si>
-  <si>
     <t xml:space="preserve">11303</t>
   </si>
   <si>
@@ -103,12 +97,6 @@
     <t xml:space="preserve">Lago Verde</t>
   </si>
   <si>
-    <t xml:space="preserve">11101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coyhaique</t>
-  </si>
-  <si>
     <t xml:space="preserve">12201</t>
   </si>
   <si>
@@ -703,6 +691,12 @@
     <t xml:space="preserve">Huechuraba</t>
   </si>
   <si>
+    <t xml:space="preserve">6204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marchihue</t>
+  </si>
+  <si>
     <t xml:space="preserve">13504</t>
   </si>
   <si>
@@ -1444,6 +1438,12 @@
     <t xml:space="preserve">San Pedro de Atacama</t>
   </si>
   <si>
+    <t xml:space="preserve">4105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paiguano</t>
+  </si>
+  <si>
     <t xml:space="preserve">2102</t>
   </si>
   <si>
@@ -2131,7 +2131,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-08 10:20</t>
+    <t xml:space="preserve">2026-09-09 20:03</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -2707,7 +2707,7 @@
         <v>15</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>97.46</v>
+        <v>97.33</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>16</v>
@@ -2739,7 +2739,7 @@
         <v>15</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>97.33</v>
+        <v>96.88</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>16</v>
@@ -2750,10 +2750,10 @@
         <v>2018</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>26</v>
@@ -2771,7 +2771,7 @@
         <v>15</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>96.88</v>
+        <v>96.58</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>16</v>
@@ -2803,7 +2803,7 @@
         <v>15</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>96.63</v>
+        <v>96.54</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>16</v>
@@ -2814,10 +2814,10 @@
         <v>2018</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>30</v>
@@ -2835,7 +2835,7 @@
         <v>15</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>96.58</v>
+        <v>96.37</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>16</v>
@@ -2846,10 +2846,10 @@
         <v>2018</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>32</v>
@@ -2867,7 +2867,7 @@
         <v>15</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>96.54</v>
+        <v>96.13</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>16</v>
@@ -2878,10 +2878,10 @@
         <v>2018</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>34</v>
@@ -2899,7 +2899,7 @@
         <v>15</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>96.37</v>
+        <v>95.84</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>16</v>
@@ -2931,7 +2931,7 @@
         <v>15</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>96.13</v>
+        <v>95.68</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>16</v>
@@ -2942,10 +2942,10 @@
         <v>2018</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>38</v>
@@ -2963,7 +2963,7 @@
         <v>15</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>95.84</v>
+        <v>95.56</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>16</v>
@@ -2974,10 +2974,10 @@
         <v>2018</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>40</v>
@@ -2995,7 +2995,7 @@
         <v>15</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>95.68</v>
+        <v>94.91</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>16</v>
@@ -3006,10 +3006,10 @@
         <v>2018</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>42</v>
@@ -3027,7 +3027,7 @@
         <v>15</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>95.56</v>
+        <v>94.69</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>16</v>
@@ -3038,28 +3038,28 @@
         <v>2018</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>94.91</v>
+        <v>98.33</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>16</v>
@@ -3070,28 +3070,28 @@
         <v>2018</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>10</v>
+        <v>49</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>94.69</v>
+        <v>98.27</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>16</v>
@@ -3102,28 +3102,28 @@
         <v>2018</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>98.33</v>
+        <v>98.12</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>16</v>
@@ -3134,28 +3134,28 @@
         <v>2018</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>98.27</v>
+        <v>98.1</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>16</v>
@@ -3166,10 +3166,10 @@
         <v>2018</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>57</v>
@@ -3178,16 +3178,16 @@
         <v>58</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>98.12</v>
+        <v>97.78</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>16</v>
@@ -3198,10 +3198,10 @@
         <v>2018</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>59</v>
@@ -3210,16 +3210,16 @@
         <v>60</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>98.1</v>
+        <v>97.62</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>16</v>
@@ -3230,10 +3230,10 @@
         <v>2018</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>61</v>
@@ -3242,16 +3242,16 @@
         <v>62</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>97.78</v>
+        <v>97.59</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>16</v>
@@ -3262,10 +3262,10 @@
         <v>2018</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>63</v>
@@ -3274,16 +3274,16 @@
         <v>64</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>97.62</v>
+        <v>97.56</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>16</v>
@@ -3297,7 +3297,7 @@
         <v>16</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>65</v>
@@ -3306,16 +3306,16 @@
         <v>66</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>97.59</v>
+        <v>97.55</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>16</v>
@@ -3326,10 +3326,10 @@
         <v>2018</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>67</v>
@@ -3338,16 +3338,16 @@
         <v>68</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>97.56</v>
+        <v>97.53</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>16</v>
@@ -3361,7 +3361,7 @@
         <v>16</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>69</v>
@@ -3370,16 +3370,16 @@
         <v>70</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>97.55</v>
+        <v>97.48</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>16</v>
@@ -3390,10 +3390,10 @@
         <v>2018</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>71</v>
@@ -3402,16 +3402,16 @@
         <v>72</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>97.53</v>
+        <v>97.36</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>16</v>
@@ -3422,10 +3422,10 @@
         <v>2018</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>73</v>
@@ -3434,16 +3434,16 @@
         <v>74</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>97.48</v>
+        <v>97.35</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>16</v>
@@ -3454,10 +3454,10 @@
         <v>2018</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>75</v>
@@ -3466,16 +3466,16 @@
         <v>76</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>97.36</v>
+        <v>97.35</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>16</v>
@@ -3489,7 +3489,7 @@
         <v>7</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>77</v>
@@ -3498,16 +3498,16 @@
         <v>78</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>97.35</v>
+        <v>97.29</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>16</v>
@@ -3518,10 +3518,10 @@
         <v>2018</v>
       </c>
       <c r="B31" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>79</v>
@@ -3530,16 +3530,16 @@
         <v>80</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>97.35</v>
+        <v>97.28</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>16</v>
@@ -3550,10 +3550,10 @@
         <v>2018</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>81</v>
@@ -3562,16 +3562,16 @@
         <v>82</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H32" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>97.29</v>
+        <v>97.28</v>
       </c>
       <c r="J32" s="2" t="s">
         <v>16</v>
@@ -3582,10 +3582,10 @@
         <v>2018</v>
       </c>
       <c r="B33" s="2" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>83</v>
@@ -3594,16 +3594,16 @@
         <v>84</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H33" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>97.28</v>
+        <v>97.23</v>
       </c>
       <c r="J33" s="2" t="s">
         <v>16</v>
@@ -3614,10 +3614,10 @@
         <v>2018</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>85</v>
@@ -3626,16 +3626,16 @@
         <v>86</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H34" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>97.28</v>
+        <v>97.22</v>
       </c>
       <c r="J34" s="2" t="s">
         <v>16</v>
@@ -3649,7 +3649,7 @@
         <v>16</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>87</v>
@@ -3658,16 +3658,16 @@
         <v>88</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H35" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>97.23</v>
+        <v>97.21</v>
       </c>
       <c r="J35" s="2" t="s">
         <v>16</v>
@@ -3678,10 +3678,10 @@
         <v>2018</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>89</v>
@@ -3690,16 +3690,16 @@
         <v>90</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H36" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>97.22</v>
+        <v>97.21</v>
       </c>
       <c r="J36" s="2" t="s">
         <v>16</v>
@@ -3710,10 +3710,10 @@
         <v>2018</v>
       </c>
       <c r="B37" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>91</v>
@@ -3722,16 +3722,16 @@
         <v>92</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H37" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>97.21</v>
+        <v>97.2</v>
       </c>
       <c r="J37" s="2" t="s">
         <v>16</v>
@@ -3742,10 +3742,10 @@
         <v>2018</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>93</v>
@@ -3754,16 +3754,16 @@
         <v>94</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H38" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>97.21</v>
+        <v>97.2</v>
       </c>
       <c r="J38" s="2" t="s">
         <v>16</v>
@@ -3774,10 +3774,10 @@
         <v>2018</v>
       </c>
       <c r="B39" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>95</v>
@@ -3786,16 +3786,16 @@
         <v>96</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H39" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>97.2</v>
+        <v>97.18</v>
       </c>
       <c r="J39" s="2" t="s">
         <v>16</v>
@@ -3806,10 +3806,10 @@
         <v>2018</v>
       </c>
       <c r="B40" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>97</v>
@@ -3818,16 +3818,16 @@
         <v>98</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H40" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>97.2</v>
+        <v>97.13</v>
       </c>
       <c r="J40" s="2" t="s">
         <v>16</v>
@@ -3841,7 +3841,7 @@
         <v>7</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>99</v>
@@ -3850,16 +3850,16 @@
         <v>100</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H41" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>97.18</v>
+        <v>97.13</v>
       </c>
       <c r="J41" s="2" t="s">
         <v>16</v>
@@ -3870,28 +3870,28 @@
         <v>2018</v>
       </c>
       <c r="B42" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>53</v>
+        <v>101</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H42" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>97.13</v>
+        <v>97.11</v>
       </c>
       <c r="J42" s="2" t="s">
         <v>16</v>
@@ -3902,28 +3902,28 @@
         <v>2018</v>
       </c>
       <c r="B43" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H43" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>97.13</v>
+        <v>97.06</v>
       </c>
       <c r="J43" s="2" t="s">
         <v>16</v>
@@ -3934,28 +3934,28 @@
         <v>2018</v>
       </c>
       <c r="B44" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H44" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>97.11</v>
+        <v>97</v>
       </c>
       <c r="J44" s="2" t="s">
         <v>16</v>
@@ -3966,28 +3966,28 @@
         <v>2018</v>
       </c>
       <c r="B45" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>53</v>
+        <v>106</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H45" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>97.06</v>
+        <v>97</v>
       </c>
       <c r="J45" s="2" t="s">
         <v>16</v>
@@ -3998,10 +3998,10 @@
         <v>2018</v>
       </c>
       <c r="B46" s="2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>110</v>
+        <v>52</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>111</v>
@@ -4010,16 +4010,16 @@
         <v>112</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H46" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>97</v>
+        <v>96.98</v>
       </c>
       <c r="J46" s="2" t="s">
         <v>16</v>
@@ -4033,7 +4033,7 @@
         <v>5</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>113</v>
@@ -4042,16 +4042,16 @@
         <v>114</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H47" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>97</v>
+        <v>96.96</v>
       </c>
       <c r="J47" s="2" t="s">
         <v>16</v>
@@ -4062,10 +4062,10 @@
         <v>2018</v>
       </c>
       <c r="B48" s="2" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>56</v>
+        <v>106</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>115</v>
@@ -4074,16 +4074,16 @@
         <v>116</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H48" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>96.98</v>
+        <v>96.95</v>
       </c>
       <c r="J48" s="2" t="s">
         <v>16</v>
@@ -4094,10 +4094,10 @@
         <v>2018</v>
       </c>
       <c r="B49" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>110</v>
+        <v>49</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>117</v>
@@ -4106,16 +4106,16 @@
         <v>118</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H49" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>96.96</v>
+        <v>96.92</v>
       </c>
       <c r="J49" s="2" t="s">
         <v>16</v>
@@ -4129,7 +4129,7 @@
         <v>5</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>119</v>
@@ -4138,16 +4138,16 @@
         <v>120</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H50" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>96.95</v>
+        <v>96.88</v>
       </c>
       <c r="J50" s="2" t="s">
         <v>16</v>
@@ -4161,7 +4161,7 @@
         <v>6</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>121</v>
@@ -4170,16 +4170,16 @@
         <v>122</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H51" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>96.92</v>
+        <v>96.87</v>
       </c>
       <c r="J51" s="2" t="s">
         <v>16</v>
@@ -4190,10 +4190,10 @@
         <v>2018</v>
       </c>
       <c r="B52" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>110</v>
+        <v>49</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>123</v>
@@ -4202,16 +4202,16 @@
         <v>124</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H52" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>96.88</v>
+        <v>96.84</v>
       </c>
       <c r="J52" s="2" t="s">
         <v>16</v>
@@ -4225,7 +4225,7 @@
         <v>6</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>125</v>
@@ -4234,16 +4234,16 @@
         <v>126</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H53" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>96.87</v>
+        <v>96.81</v>
       </c>
       <c r="J53" s="2" t="s">
         <v>16</v>
@@ -4254,10 +4254,10 @@
         <v>2018</v>
       </c>
       <c r="B54" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>127</v>
@@ -4266,16 +4266,16 @@
         <v>128</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H54" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>96.84</v>
+        <v>96.81</v>
       </c>
       <c r="J54" s="2" t="s">
         <v>16</v>
@@ -4289,7 +4289,7 @@
         <v>6</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>129</v>
@@ -4298,16 +4298,16 @@
         <v>130</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H55" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>96.81</v>
+        <v>96.78</v>
       </c>
       <c r="J55" s="2" t="s">
         <v>16</v>
@@ -4318,10 +4318,10 @@
         <v>2018</v>
       </c>
       <c r="B56" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>131</v>
@@ -4330,16 +4330,16 @@
         <v>132</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H56" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>96.81</v>
+        <v>96.76</v>
       </c>
       <c r="J56" s="2" t="s">
         <v>16</v>
@@ -4350,10 +4350,10 @@
         <v>2018</v>
       </c>
       <c r="B57" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>133</v>
@@ -4362,16 +4362,16 @@
         <v>134</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H57" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>96.78</v>
+        <v>96.76</v>
       </c>
       <c r="J57" s="2" t="s">
         <v>16</v>
@@ -4382,10 +4382,10 @@
         <v>2018</v>
       </c>
       <c r="B58" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>135</v>
@@ -4394,16 +4394,16 @@
         <v>136</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H58" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>96.76</v>
+        <v>96.75</v>
       </c>
       <c r="J58" s="2" t="s">
         <v>16</v>
@@ -4417,7 +4417,7 @@
         <v>7</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>137</v>
@@ -4426,16 +4426,16 @@
         <v>138</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H59" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>96.76</v>
+        <v>96.71</v>
       </c>
       <c r="J59" s="2" t="s">
         <v>16</v>
@@ -4449,7 +4449,7 @@
         <v>7</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>139</v>
@@ -4458,16 +4458,16 @@
         <v>140</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H60" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>96.75</v>
+        <v>96.68</v>
       </c>
       <c r="J60" s="2" t="s">
         <v>16</v>
@@ -4478,10 +4478,10 @@
         <v>2018</v>
       </c>
       <c r="B61" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>48</v>
+        <v>106</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>141</v>
@@ -4490,16 +4490,16 @@
         <v>142</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H61" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>96.71</v>
+        <v>96.67</v>
       </c>
       <c r="J61" s="2" t="s">
         <v>16</v>
@@ -4510,10 +4510,10 @@
         <v>2018</v>
       </c>
       <c r="B62" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>48</v>
+        <v>106</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>143</v>
@@ -4522,16 +4522,16 @@
         <v>144</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H62" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>96.68</v>
+        <v>96.67</v>
       </c>
       <c r="J62" s="2" t="s">
         <v>16</v>
@@ -4542,10 +4542,10 @@
         <v>2018</v>
       </c>
       <c r="B63" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>110</v>
+        <v>49</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>145</v>
@@ -4554,10 +4554,10 @@
         <v>146</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H63" s="2" t="s">
         <v>15</v>
@@ -4574,10 +4574,10 @@
         <v>2018</v>
       </c>
       <c r="B64" s="2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>110</v>
+        <v>52</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>147</v>
@@ -4586,10 +4586,10 @@
         <v>148</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H64" s="2" t="s">
         <v>15</v>
@@ -4609,7 +4609,7 @@
         <v>6</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>149</v>
@@ -4618,16 +4618,16 @@
         <v>150</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H65" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>96.67</v>
+        <v>96.66</v>
       </c>
       <c r="J65" s="2" t="s">
         <v>16</v>
@@ -4638,10 +4638,10 @@
         <v>2018</v>
       </c>
       <c r="B66" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>151</v>
@@ -4650,16 +4650,16 @@
         <v>152</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H66" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>96.67</v>
+        <v>96.63</v>
       </c>
       <c r="J66" s="2" t="s">
         <v>16</v>
@@ -4670,10 +4670,10 @@
         <v>2018</v>
       </c>
       <c r="B67" s="2" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>153</v>
@@ -4682,16 +4682,16 @@
         <v>154</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H67" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>96.66</v>
+        <v>96.62</v>
       </c>
       <c r="J67" s="2" t="s">
         <v>16</v>
@@ -4702,10 +4702,10 @@
         <v>2018</v>
       </c>
       <c r="B68" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>155</v>
@@ -4714,16 +4714,16 @@
         <v>156</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H68" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>96.63</v>
+        <v>96.59</v>
       </c>
       <c r="J68" s="2" t="s">
         <v>16</v>
@@ -4734,10 +4734,10 @@
         <v>2018</v>
       </c>
       <c r="B69" s="2" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>56</v>
+        <v>106</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>157</v>
@@ -4746,16 +4746,16 @@
         <v>158</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H69" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>96.62</v>
+        <v>96.58</v>
       </c>
       <c r="J69" s="2" t="s">
         <v>16</v>
@@ -4769,7 +4769,7 @@
         <v>6</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>159</v>
@@ -4778,16 +4778,16 @@
         <v>160</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H70" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>96.59</v>
+        <v>96.53</v>
       </c>
       <c r="J70" s="2" t="s">
         <v>16</v>
@@ -4798,10 +4798,10 @@
         <v>2018</v>
       </c>
       <c r="B71" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>110</v>
+        <v>44</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>161</v>
@@ -4810,16 +4810,16 @@
         <v>162</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H71" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>96.58</v>
+        <v>96.51</v>
       </c>
       <c r="J71" s="2" t="s">
         <v>16</v>
@@ -4830,10 +4830,10 @@
         <v>2018</v>
       </c>
       <c r="B72" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>163</v>
@@ -4842,16 +4842,16 @@
         <v>164</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H72" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>96.53</v>
+        <v>96.48</v>
       </c>
       <c r="J72" s="2" t="s">
         <v>16</v>
@@ -4865,7 +4865,7 @@
         <v>7</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>165</v>
@@ -4874,16 +4874,16 @@
         <v>166</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H73" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>96.51</v>
+        <v>96.47</v>
       </c>
       <c r="J73" s="2" t="s">
         <v>16</v>
@@ -4897,7 +4897,7 @@
         <v>7</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>167</v>
@@ -4906,16 +4906,16 @@
         <v>168</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H74" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>96.48</v>
+        <v>96.44</v>
       </c>
       <c r="J74" s="2" t="s">
         <v>16</v>
@@ -4929,7 +4929,7 @@
         <v>7</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>169</v>
@@ -4938,16 +4938,16 @@
         <v>170</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H75" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>96.47</v>
+        <v>96.44</v>
       </c>
       <c r="J75" s="2" t="s">
         <v>16</v>
@@ -4961,7 +4961,7 @@
         <v>7</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>171</v>
@@ -4970,10 +4970,10 @@
         <v>172</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H76" s="2" t="s">
         <v>15</v>
@@ -4993,7 +4993,7 @@
         <v>7</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>173</v>
@@ -5002,16 +5002,16 @@
         <v>174</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H77" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>96.44</v>
+        <v>96.42</v>
       </c>
       <c r="J77" s="2" t="s">
         <v>16</v>
@@ -5022,10 +5022,10 @@
         <v>2018</v>
       </c>
       <c r="B78" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>175</v>
@@ -5034,16 +5034,16 @@
         <v>176</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H78" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>96.44</v>
+        <v>96.41</v>
       </c>
       <c r="J78" s="2" t="s">
         <v>16</v>
@@ -5054,10 +5054,10 @@
         <v>2018</v>
       </c>
       <c r="B79" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>48</v>
+        <v>101</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>177</v>
@@ -5066,16 +5066,16 @@
         <v>178</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H79" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>96.42</v>
+        <v>96.4</v>
       </c>
       <c r="J79" s="2" t="s">
         <v>16</v>
@@ -5086,28 +5086,28 @@
         <v>2018</v>
       </c>
       <c r="B80" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>179</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>180</v>
+        <v>44</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H80" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>96.41</v>
+        <v>96.4</v>
       </c>
       <c r="J80" s="2" t="s">
         <v>16</v>
@@ -5118,28 +5118,28 @@
         <v>2018</v>
       </c>
       <c r="B81" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D81" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="E81" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="E81" s="2" t="s">
-        <v>182</v>
-      </c>
       <c r="F81" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H81" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>96.4</v>
+        <v>96.39</v>
       </c>
       <c r="J81" s="2" t="s">
         <v>16</v>
@@ -5150,28 +5150,28 @@
         <v>2018</v>
       </c>
       <c r="B82" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D82" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="E82" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="E82" s="2" t="s">
-        <v>48</v>
-      </c>
       <c r="F82" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H82" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>96.4</v>
+        <v>96.38</v>
       </c>
       <c r="J82" s="2" t="s">
         <v>16</v>
@@ -5182,10 +5182,10 @@
         <v>2018</v>
       </c>
       <c r="B83" s="2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>110</v>
+        <v>52</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>184</v>
@@ -5194,16 +5194,16 @@
         <v>185</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H83" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>96.39</v>
+        <v>96.37</v>
       </c>
       <c r="J83" s="2" t="s">
         <v>16</v>
@@ -5214,10 +5214,10 @@
         <v>2018</v>
       </c>
       <c r="B84" s="2" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D84" s="2" t="s">
         <v>186</v>
@@ -5226,16 +5226,16 @@
         <v>187</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H84" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>96.38</v>
+        <v>96.35</v>
       </c>
       <c r="J84" s="2" t="s">
         <v>16</v>
@@ -5249,7 +5249,7 @@
         <v>16</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D85" s="2" t="s">
         <v>188</v>
@@ -5258,16 +5258,16 @@
         <v>189</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H85" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>96.37</v>
+        <v>96.34</v>
       </c>
       <c r="J85" s="2" t="s">
         <v>16</v>
@@ -5278,10 +5278,10 @@
         <v>2018</v>
       </c>
       <c r="B86" s="2" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>56</v>
+        <v>106</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>190</v>
@@ -5290,16 +5290,16 @@
         <v>191</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H86" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>96.35</v>
+        <v>96.32</v>
       </c>
       <c r="J86" s="2" t="s">
         <v>16</v>
@@ -5310,10 +5310,10 @@
         <v>2018</v>
       </c>
       <c r="B87" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>192</v>
@@ -5322,16 +5322,16 @@
         <v>193</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H87" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>96.34</v>
+        <v>96.32</v>
       </c>
       <c r="J87" s="2" t="s">
         <v>16</v>
@@ -5345,7 +5345,7 @@
         <v>5</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>194</v>
@@ -5354,16 +5354,16 @@
         <v>195</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H88" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>96.32</v>
+        <v>96.3</v>
       </c>
       <c r="J88" s="2" t="s">
         <v>16</v>
@@ -5374,10 +5374,10 @@
         <v>2018</v>
       </c>
       <c r="B89" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>196</v>
@@ -5386,16 +5386,16 @@
         <v>197</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H89" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>96.32</v>
+        <v>96.3</v>
       </c>
       <c r="J89" s="2" t="s">
         <v>16</v>
@@ -5409,7 +5409,7 @@
         <v>5</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D90" s="2" t="s">
         <v>198</v>
@@ -5418,16 +5418,16 @@
         <v>199</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H90" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>96.3</v>
+        <v>96.28</v>
       </c>
       <c r="J90" s="2" t="s">
         <v>16</v>
@@ -5438,10 +5438,10 @@
         <v>2018</v>
       </c>
       <c r="B91" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>53</v>
+        <v>106</v>
       </c>
       <c r="D91" s="2" t="s">
         <v>200</v>
@@ -5450,16 +5450,16 @@
         <v>201</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H91" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>96.3</v>
+        <v>96.27</v>
       </c>
       <c r="J91" s="2" t="s">
         <v>16</v>
@@ -5470,10 +5470,10 @@
         <v>2018</v>
       </c>
       <c r="B92" s="2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>110</v>
+        <v>52</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>202</v>
@@ -5482,16 +5482,16 @@
         <v>203</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H92" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>96.28</v>
+        <v>96.27</v>
       </c>
       <c r="J92" s="2" t="s">
         <v>16</v>
@@ -5502,10 +5502,10 @@
         <v>2018</v>
       </c>
       <c r="B93" s="2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>110</v>
+        <v>52</v>
       </c>
       <c r="D93" s="2" t="s">
         <v>204</v>
@@ -5514,16 +5514,16 @@
         <v>205</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H93" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>96.27</v>
+        <v>96.22</v>
       </c>
       <c r="J93" s="2" t="s">
         <v>16</v>
@@ -5534,10 +5534,10 @@
         <v>2018</v>
       </c>
       <c r="B94" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="D94" s="2" t="s">
         <v>206</v>
@@ -5546,16 +5546,16 @@
         <v>207</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H94" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>96.27</v>
+        <v>96.2</v>
       </c>
       <c r="J94" s="2" t="s">
         <v>16</v>
@@ -5566,10 +5566,10 @@
         <v>2018</v>
       </c>
       <c r="B95" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>56</v>
+        <v>101</v>
       </c>
       <c r="D95" s="2" t="s">
         <v>208</v>
@@ -5578,16 +5578,16 @@
         <v>209</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H95" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>96.22</v>
+        <v>96.18</v>
       </c>
       <c r="J95" s="2" t="s">
         <v>16</v>
@@ -5598,10 +5598,10 @@
         <v>2018</v>
       </c>
       <c r="B96" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>53</v>
+        <v>106</v>
       </c>
       <c r="D96" s="2" t="s">
         <v>210</v>
@@ -5610,16 +5610,16 @@
         <v>211</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H96" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>96.2</v>
+        <v>96.12</v>
       </c>
       <c r="J96" s="2" t="s">
         <v>16</v>
@@ -5633,7 +5633,7 @@
         <v>13</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D97" s="2" t="s">
         <v>212</v>
@@ -5642,16 +5642,16 @@
         <v>213</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H97" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>96.18</v>
+        <v>96.08</v>
       </c>
       <c r="J97" s="2" t="s">
         <v>16</v>
@@ -5662,10 +5662,10 @@
         <v>2018</v>
       </c>
       <c r="B98" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>110</v>
+        <v>44</v>
       </c>
       <c r="D98" s="2" t="s">
         <v>214</v>
@@ -5674,16 +5674,16 @@
         <v>215</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H98" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>96.12</v>
+        <v>96.04</v>
       </c>
       <c r="J98" s="2" t="s">
         <v>16</v>
@@ -5694,10 +5694,10 @@
         <v>2018</v>
       </c>
       <c r="B99" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D99" s="2" t="s">
         <v>216</v>
@@ -5706,16 +5706,16 @@
         <v>217</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H99" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>96.08</v>
+        <v>96.03</v>
       </c>
       <c r="J99" s="2" t="s">
         <v>16</v>
@@ -5726,10 +5726,10 @@
         <v>2018</v>
       </c>
       <c r="B100" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>48</v>
+        <v>106</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>218</v>
@@ -5738,16 +5738,16 @@
         <v>219</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H100" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>96.04</v>
+        <v>96.02</v>
       </c>
       <c r="J100" s="2" t="s">
         <v>16</v>
@@ -5761,7 +5761,7 @@
         <v>5</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D101" s="2" t="s">
         <v>220</v>
@@ -5770,16 +5770,16 @@
         <v>221</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H101" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>96.03</v>
+        <v>96</v>
       </c>
       <c r="J101" s="2" t="s">
         <v>16</v>
@@ -5790,10 +5790,10 @@
         <v>2018</v>
       </c>
       <c r="B102" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="D102" s="2" t="s">
         <v>222</v>
@@ -5802,16 +5802,16 @@
         <v>223</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H102" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>96.02</v>
+        <v>96</v>
       </c>
       <c r="J102" s="2" t="s">
         <v>16</v>
@@ -5822,10 +5822,10 @@
         <v>2018</v>
       </c>
       <c r="B103" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>110</v>
+        <v>49</v>
       </c>
       <c r="D103" s="2" t="s">
         <v>224</v>
@@ -5834,16 +5834,16 @@
         <v>225</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H103" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>96</v>
+        <v>95.95</v>
       </c>
       <c r="J103" s="2" t="s">
         <v>16</v>
@@ -5857,7 +5857,7 @@
         <v>13</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D104" s="2" t="s">
         <v>226</v>
@@ -5866,16 +5866,16 @@
         <v>227</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H104" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>96</v>
+        <v>95.92</v>
       </c>
       <c r="J104" s="2" t="s">
         <v>16</v>
@@ -5886,10 +5886,10 @@
         <v>2018</v>
       </c>
       <c r="B105" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>105</v>
+        <v>49</v>
       </c>
       <c r="D105" s="2" t="s">
         <v>228</v>
@@ -5898,10 +5898,10 @@
         <v>229</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H105" s="2" t="s">
         <v>15</v>
@@ -5918,10 +5918,10 @@
         <v>2018</v>
       </c>
       <c r="B106" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>53</v>
+        <v>106</v>
       </c>
       <c r="D106" s="2" t="s">
         <v>230</v>
@@ -5930,16 +5930,16 @@
         <v>231</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H106" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>95.92</v>
+        <v>95.89</v>
       </c>
       <c r="J106" s="2" t="s">
         <v>16</v>
@@ -5950,10 +5950,10 @@
         <v>2018</v>
       </c>
       <c r="B107" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="D107" s="2" t="s">
         <v>232</v>
@@ -5962,10 +5962,10 @@
         <v>233</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H107" s="2" t="s">
         <v>15</v>
@@ -5982,10 +5982,10 @@
         <v>2018</v>
       </c>
       <c r="B108" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>105</v>
+        <v>52</v>
       </c>
       <c r="D108" s="2" t="s">
         <v>234</v>
@@ -5994,16 +5994,16 @@
         <v>235</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H108" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>95.89</v>
+        <v>95.86</v>
       </c>
       <c r="J108" s="2" t="s">
         <v>16</v>
@@ -6014,10 +6014,10 @@
         <v>2018</v>
       </c>
       <c r="B109" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>56</v>
+        <v>101</v>
       </c>
       <c r="D109" s="2" t="s">
         <v>236</v>
@@ -6026,16 +6026,16 @@
         <v>237</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H109" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>95.86</v>
+        <v>95.84</v>
       </c>
       <c r="J109" s="2" t="s">
         <v>16</v>
@@ -6046,10 +6046,10 @@
         <v>2018</v>
       </c>
       <c r="B110" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>105</v>
+        <v>49</v>
       </c>
       <c r="D110" s="2" t="s">
         <v>238</v>
@@ -6058,10 +6058,10 @@
         <v>239</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H110" s="2" t="s">
         <v>15</v>
@@ -6081,7 +6081,7 @@
         <v>6</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D111" s="2" t="s">
         <v>240</v>
@@ -6090,16 +6090,16 @@
         <v>241</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H111" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>95.84</v>
+        <v>95.8</v>
       </c>
       <c r="J111" s="2" t="s">
         <v>16</v>
@@ -6113,7 +6113,7 @@
         <v>6</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D112" s="2" t="s">
         <v>242</v>
@@ -6122,10 +6122,10 @@
         <v>243</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H112" s="2" t="s">
         <v>15</v>
@@ -6142,10 +6142,10 @@
         <v>2018</v>
       </c>
       <c r="B113" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>53</v>
+        <v>101</v>
       </c>
       <c r="D113" s="2" t="s">
         <v>244</v>
@@ -6154,16 +6154,16 @@
         <v>245</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H113" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>95.8</v>
+        <v>95.79</v>
       </c>
       <c r="J113" s="2" t="s">
         <v>16</v>
@@ -6177,7 +6177,7 @@
         <v>13</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D114" s="2" t="s">
         <v>246</v>
@@ -6186,16 +6186,16 @@
         <v>247</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H114" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>95.79</v>
+        <v>95.78</v>
       </c>
       <c r="J114" s="2" t="s">
         <v>16</v>
@@ -6209,7 +6209,7 @@
         <v>13</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D115" s="2" t="s">
         <v>248</v>
@@ -6218,16 +6218,16 @@
         <v>249</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H115" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>95.78</v>
+        <v>95.77</v>
       </c>
       <c r="J115" s="2" t="s">
         <v>16</v>
@@ -6238,10 +6238,10 @@
         <v>2018</v>
       </c>
       <c r="B116" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>105</v>
+        <v>44</v>
       </c>
       <c r="D116" s="2" t="s">
         <v>250</v>
@@ -6250,10 +6250,10 @@
         <v>251</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H116" s="2" t="s">
         <v>15</v>
@@ -6270,10 +6270,10 @@
         <v>2018</v>
       </c>
       <c r="B117" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D117" s="2" t="s">
         <v>252</v>
@@ -6282,16 +6282,16 @@
         <v>253</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H117" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>95.77</v>
+        <v>95.76</v>
       </c>
       <c r="J117" s="2" t="s">
         <v>16</v>
@@ -6302,10 +6302,10 @@
         <v>2018</v>
       </c>
       <c r="B118" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>53</v>
+        <v>106</v>
       </c>
       <c r="D118" s="2" t="s">
         <v>254</v>
@@ -6314,16 +6314,16 @@
         <v>255</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H118" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>95.76</v>
+        <v>95.74</v>
       </c>
       <c r="J118" s="2" t="s">
         <v>16</v>
@@ -6334,10 +6334,10 @@
         <v>2018</v>
       </c>
       <c r="B119" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="D119" s="2" t="s">
         <v>256</v>
@@ -6346,16 +6346,16 @@
         <v>257</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H119" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>95.74</v>
+        <v>95.72</v>
       </c>
       <c r="J119" s="2" t="s">
         <v>16</v>
@@ -6366,10 +6366,10 @@
         <v>2018</v>
       </c>
       <c r="B120" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>105</v>
+        <v>52</v>
       </c>
       <c r="D120" s="2" t="s">
         <v>258</v>
@@ -6378,16 +6378,16 @@
         <v>259</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H120" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>95.72</v>
+        <v>95.68</v>
       </c>
       <c r="J120" s="2" t="s">
         <v>16</v>
@@ -6398,10 +6398,10 @@
         <v>2018</v>
       </c>
       <c r="B121" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>56</v>
+        <v>101</v>
       </c>
       <c r="D121" s="2" t="s">
         <v>260</v>
@@ -6410,16 +6410,16 @@
         <v>261</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G121" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H121" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>95.68</v>
+        <v>95.66</v>
       </c>
       <c r="J121" s="2" t="s">
         <v>16</v>
@@ -6430,10 +6430,10 @@
         <v>2018</v>
       </c>
       <c r="B122" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D122" s="2" t="s">
         <v>262</v>
@@ -6442,16 +6442,16 @@
         <v>263</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H122" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>95.66</v>
+        <v>95.63</v>
       </c>
       <c r="J122" s="2" t="s">
         <v>16</v>
@@ -6462,10 +6462,10 @@
         <v>2018</v>
       </c>
       <c r="B123" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>110</v>
+        <v>44</v>
       </c>
       <c r="D123" s="2" t="s">
         <v>264</v>
@@ -6474,16 +6474,16 @@
         <v>265</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G123" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H123" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>95.63</v>
+        <v>95.57</v>
       </c>
       <c r="J123" s="2" t="s">
         <v>16</v>
@@ -6497,7 +6497,7 @@
         <v>7</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D124" s="2" t="s">
         <v>266</v>
@@ -6506,10 +6506,10 @@
         <v>267</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G124" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H124" s="2" t="s">
         <v>15</v>
@@ -6526,10 +6526,10 @@
         <v>2018</v>
       </c>
       <c r="B125" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>48</v>
+        <v>106</v>
       </c>
       <c r="D125" s="2" t="s">
         <v>268</v>
@@ -6538,16 +6538,16 @@
         <v>269</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G125" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H125" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>95.57</v>
+        <v>95.54</v>
       </c>
       <c r="J125" s="2" t="s">
         <v>16</v>
@@ -6558,10 +6558,10 @@
         <v>2018</v>
       </c>
       <c r="B126" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="D126" s="2" t="s">
         <v>270</v>
@@ -6570,10 +6570,10 @@
         <v>271</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G126" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H126" s="2" t="s">
         <v>15</v>
@@ -6590,10 +6590,10 @@
         <v>2018</v>
       </c>
       <c r="B127" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>105</v>
+        <v>49</v>
       </c>
       <c r="D127" s="2" t="s">
         <v>272</v>
@@ -6602,16 +6602,16 @@
         <v>273</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G127" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H127" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>95.54</v>
+        <v>95.51</v>
       </c>
       <c r="J127" s="2" t="s">
         <v>16</v>
@@ -6622,10 +6622,10 @@
         <v>2018</v>
       </c>
       <c r="B128" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>53</v>
+        <v>106</v>
       </c>
       <c r="D128" s="2" t="s">
         <v>274</v>
@@ -6634,16 +6634,16 @@
         <v>275</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H128" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>95.51</v>
+        <v>95.49</v>
       </c>
       <c r="J128" s="2" t="s">
         <v>16</v>
@@ -6654,10 +6654,10 @@
         <v>2018</v>
       </c>
       <c r="B129" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="D129" s="2" t="s">
         <v>276</v>
@@ -6666,10 +6666,10 @@
         <v>277</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G129" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H129" s="2" t="s">
         <v>15</v>
@@ -6689,7 +6689,7 @@
         <v>13</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D130" s="2" t="s">
         <v>278</v>
@@ -6698,16 +6698,16 @@
         <v>279</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G130" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H130" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I130" s="2" t="n">
-        <v>95.49</v>
+        <v>95.46</v>
       </c>
       <c r="J130" s="2" t="s">
         <v>16</v>
@@ -6721,7 +6721,7 @@
         <v>13</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D131" s="2" t="s">
         <v>280</v>
@@ -6730,16 +6730,16 @@
         <v>281</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G131" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H131" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I131" s="2" t="n">
-        <v>95.46</v>
+        <v>95.45</v>
       </c>
       <c r="J131" s="2" t="s">
         <v>16</v>
@@ -6753,7 +6753,7 @@
         <v>13</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D132" s="2" t="s">
         <v>282</v>
@@ -6762,16 +6762,16 @@
         <v>283</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G132" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H132" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I132" s="2" t="n">
-        <v>95.45</v>
+        <v>95.39</v>
       </c>
       <c r="J132" s="2" t="s">
         <v>16</v>
@@ -6785,7 +6785,7 @@
         <v>13</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D133" s="2" t="s">
         <v>284</v>
@@ -6794,16 +6794,16 @@
         <v>285</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G133" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H133" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I133" s="2" t="n">
-        <v>95.39</v>
+        <v>95.38</v>
       </c>
       <c r="J133" s="2" t="s">
         <v>16</v>
@@ -6817,7 +6817,7 @@
         <v>13</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D134" s="2" t="s">
         <v>286</v>
@@ -6826,10 +6826,10 @@
         <v>287</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G134" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H134" s="2" t="s">
         <v>15</v>
@@ -6846,10 +6846,10 @@
         <v>2018</v>
       </c>
       <c r="B135" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>105</v>
+        <v>52</v>
       </c>
       <c r="D135" s="2" t="s">
         <v>288</v>
@@ -6858,16 +6858,16 @@
         <v>289</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G135" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H135" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I135" s="2" t="n">
-        <v>95.38</v>
+        <v>95.37</v>
       </c>
       <c r="J135" s="2" t="s">
         <v>16</v>
@@ -6878,10 +6878,10 @@
         <v>2018</v>
       </c>
       <c r="B136" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>56</v>
+        <v>101</v>
       </c>
       <c r="D136" s="2" t="s">
         <v>290</v>
@@ -6890,16 +6890,16 @@
         <v>291</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G136" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H136" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I136" s="2" t="n">
-        <v>95.37</v>
+        <v>95.32</v>
       </c>
       <c r="J136" s="2" t="s">
         <v>16</v>
@@ -6913,7 +6913,7 @@
         <v>13</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D137" s="2" t="s">
         <v>292</v>
@@ -6922,16 +6922,16 @@
         <v>293</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G137" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H137" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I137" s="2" t="n">
-        <v>95.32</v>
+        <v>95.27</v>
       </c>
       <c r="J137" s="2" t="s">
         <v>16</v>
@@ -6942,10 +6942,10 @@
         <v>2018</v>
       </c>
       <c r="B138" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>105</v>
+        <v>49</v>
       </c>
       <c r="D138" s="2" t="s">
         <v>294</v>
@@ -6954,16 +6954,16 @@
         <v>295</v>
       </c>
       <c r="F138" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G138" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H138" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I138" s="2" t="n">
-        <v>95.27</v>
+        <v>95.25</v>
       </c>
       <c r="J138" s="2" t="s">
         <v>16</v>
@@ -6974,10 +6974,10 @@
         <v>2018</v>
       </c>
       <c r="B139" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>53</v>
+        <v>101</v>
       </c>
       <c r="D139" s="2" t="s">
         <v>296</v>
@@ -6986,16 +6986,16 @@
         <v>297</v>
       </c>
       <c r="F139" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G139" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H139" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I139" s="2" t="n">
-        <v>95.25</v>
+        <v>95.19</v>
       </c>
       <c r="J139" s="2" t="s">
         <v>16</v>
@@ -7009,7 +7009,7 @@
         <v>13</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D140" s="2" t="s">
         <v>298</v>
@@ -7018,16 +7018,16 @@
         <v>299</v>
       </c>
       <c r="F140" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G140" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H140" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I140" s="2" t="n">
-        <v>95.19</v>
+        <v>95.09</v>
       </c>
       <c r="J140" s="2" t="s">
         <v>16</v>
@@ -7041,7 +7041,7 @@
         <v>13</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D141" s="2" t="s">
         <v>300</v>
@@ -7050,16 +7050,16 @@
         <v>301</v>
       </c>
       <c r="F141" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G141" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H141" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I141" s="2" t="n">
-        <v>95.09</v>
+        <v>95.06</v>
       </c>
       <c r="J141" s="2" t="s">
         <v>16</v>
@@ -7073,7 +7073,7 @@
         <v>13</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D142" s="2" t="s">
         <v>302</v>
@@ -7082,16 +7082,16 @@
         <v>303</v>
       </c>
       <c r="F142" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G142" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H142" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I142" s="2" t="n">
-        <v>95.06</v>
+        <v>95.03</v>
       </c>
       <c r="J142" s="2" t="s">
         <v>16</v>
@@ -7102,10 +7102,10 @@
         <v>2018</v>
       </c>
       <c r="B143" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D143" s="2" t="s">
         <v>304</v>
@@ -7114,16 +7114,16 @@
         <v>305</v>
       </c>
       <c r="F143" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G143" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H143" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I143" s="2" t="n">
-        <v>95.03</v>
+        <v>95.02</v>
       </c>
       <c r="J143" s="2" t="s">
         <v>16</v>
@@ -7134,10 +7134,10 @@
         <v>2018</v>
       </c>
       <c r="B144" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="D144" s="2" t="s">
         <v>306</v>
@@ -7146,16 +7146,16 @@
         <v>307</v>
       </c>
       <c r="F144" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G144" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H144" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I144" s="2" t="n">
-        <v>95.02</v>
+        <v>95</v>
       </c>
       <c r="J144" s="2" t="s">
         <v>16</v>
@@ -7166,10 +7166,10 @@
         <v>2018</v>
       </c>
       <c r="B145" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>105</v>
+        <v>49</v>
       </c>
       <c r="D145" s="2" t="s">
         <v>308</v>
@@ -7178,16 +7178,16 @@
         <v>309</v>
       </c>
       <c r="F145" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G145" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H145" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I145" s="2" t="n">
-        <v>95</v>
+        <v>94.97</v>
       </c>
       <c r="J145" s="2" t="s">
         <v>16</v>
@@ -7198,10 +7198,10 @@
         <v>2018</v>
       </c>
       <c r="B146" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>53</v>
+        <v>106</v>
       </c>
       <c r="D146" s="2" t="s">
         <v>310</v>
@@ -7210,16 +7210,16 @@
         <v>311</v>
       </c>
       <c r="F146" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G146" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H146" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I146" s="2" t="n">
-        <v>94.97</v>
+        <v>94.96</v>
       </c>
       <c r="J146" s="2" t="s">
         <v>16</v>
@@ -7230,10 +7230,10 @@
         <v>2018</v>
       </c>
       <c r="B147" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>110</v>
+        <v>44</v>
       </c>
       <c r="D147" s="2" t="s">
         <v>312</v>
@@ -7242,16 +7242,16 @@
         <v>313</v>
       </c>
       <c r="F147" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G147" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H147" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I147" s="2" t="n">
-        <v>94.96</v>
+        <v>94.95</v>
       </c>
       <c r="J147" s="2" t="s">
         <v>16</v>
@@ -7262,10 +7262,10 @@
         <v>2018</v>
       </c>
       <c r="B148" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>48</v>
+        <v>101</v>
       </c>
       <c r="D148" s="2" t="s">
         <v>314</v>
@@ -7274,16 +7274,16 @@
         <v>315</v>
       </c>
       <c r="F148" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G148" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H148" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I148" s="2" t="n">
-        <v>94.95</v>
+        <v>94.94</v>
       </c>
       <c r="J148" s="2" t="s">
         <v>16</v>
@@ -7294,10 +7294,10 @@
         <v>2018</v>
       </c>
       <c r="B149" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D149" s="2" t="s">
         <v>316</v>
@@ -7306,16 +7306,16 @@
         <v>317</v>
       </c>
       <c r="F149" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G149" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H149" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I149" s="2" t="n">
-        <v>94.94</v>
+        <v>94.92</v>
       </c>
       <c r="J149" s="2" t="s">
         <v>16</v>
@@ -7329,7 +7329,7 @@
         <v>5</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D150" s="2" t="s">
         <v>318</v>
@@ -7338,16 +7338,16 @@
         <v>319</v>
       </c>
       <c r="F150" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G150" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H150" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I150" s="2" t="n">
-        <v>94.92</v>
+        <v>94.91</v>
       </c>
       <c r="J150" s="2" t="s">
         <v>16</v>
@@ -7358,10 +7358,10 @@
         <v>2018</v>
       </c>
       <c r="B151" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="D151" s="2" t="s">
         <v>320</v>
@@ -7370,16 +7370,16 @@
         <v>321</v>
       </c>
       <c r="F151" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G151" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H151" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I151" s="2" t="n">
-        <v>94.91</v>
+        <v>94.84</v>
       </c>
       <c r="J151" s="2" t="s">
         <v>16</v>
@@ -7393,7 +7393,7 @@
         <v>13</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D152" s="2" t="s">
         <v>322</v>
@@ -7402,16 +7402,16 @@
         <v>323</v>
       </c>
       <c r="F152" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G152" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H152" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I152" s="2" t="n">
-        <v>94.84</v>
+        <v>94.77</v>
       </c>
       <c r="J152" s="2" t="s">
         <v>16</v>
@@ -7422,10 +7422,10 @@
         <v>2018</v>
       </c>
       <c r="B153" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>105</v>
+        <v>49</v>
       </c>
       <c r="D153" s="2" t="s">
         <v>324</v>
@@ -7434,16 +7434,16 @@
         <v>325</v>
       </c>
       <c r="F153" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G153" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H153" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I153" s="2" t="n">
-        <v>94.77</v>
+        <v>94.73</v>
       </c>
       <c r="J153" s="2" t="s">
         <v>16</v>
@@ -7454,10 +7454,10 @@
         <v>2018</v>
       </c>
       <c r="B154" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>53</v>
+        <v>101</v>
       </c>
       <c r="D154" s="2" t="s">
         <v>326</v>
@@ -7466,16 +7466,16 @@
         <v>327</v>
       </c>
       <c r="F154" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G154" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H154" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I154" s="2" t="n">
-        <v>94.73</v>
+        <v>94.7</v>
       </c>
       <c r="J154" s="2" t="s">
         <v>16</v>
@@ -7489,7 +7489,7 @@
         <v>13</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D155" s="2" t="s">
         <v>328</v>
@@ -7498,16 +7498,16 @@
         <v>329</v>
       </c>
       <c r="F155" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G155" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H155" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I155" s="2" t="n">
-        <v>94.7</v>
+        <v>94.63</v>
       </c>
       <c r="J155" s="2" t="s">
         <v>16</v>
@@ -7518,10 +7518,10 @@
         <v>2018</v>
       </c>
       <c r="B156" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D156" s="2" t="s">
         <v>330</v>
@@ -7530,16 +7530,16 @@
         <v>331</v>
       </c>
       <c r="F156" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G156" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H156" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I156" s="2" t="n">
-        <v>94.63</v>
+        <v>94.57</v>
       </c>
       <c r="J156" s="2" t="s">
         <v>16</v>
@@ -7553,7 +7553,7 @@
         <v>5</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D157" s="2" t="s">
         <v>332</v>
@@ -7562,16 +7562,16 @@
         <v>333</v>
       </c>
       <c r="F157" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G157" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H157" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I157" s="2" t="n">
-        <v>94.57</v>
+        <v>94.54</v>
       </c>
       <c r="J157" s="2" t="s">
         <v>16</v>
@@ -7585,7 +7585,7 @@
         <v>5</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D158" s="2" t="s">
         <v>334</v>
@@ -7594,16 +7594,16 @@
         <v>335</v>
       </c>
       <c r="F158" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G158" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H158" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I158" s="2" t="n">
-        <v>94.54</v>
+        <v>94.53</v>
       </c>
       <c r="J158" s="2" t="s">
         <v>16</v>
@@ -7614,10 +7614,10 @@
         <v>2018</v>
       </c>
       <c r="B159" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="D159" s="2" t="s">
         <v>336</v>
@@ -7626,16 +7626,16 @@
         <v>337</v>
       </c>
       <c r="F159" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G159" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H159" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I159" s="2" t="n">
-        <v>94.53</v>
+        <v>94.48</v>
       </c>
       <c r="J159" s="2" t="s">
         <v>16</v>
@@ -7649,7 +7649,7 @@
         <v>13</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D160" s="2" t="s">
         <v>338</v>
@@ -7658,10 +7658,10 @@
         <v>339</v>
       </c>
       <c r="F160" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G160" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H160" s="2" t="s">
         <v>15</v>
@@ -7681,7 +7681,7 @@
         <v>13</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D161" s="2" t="s">
         <v>340</v>
@@ -7690,16 +7690,16 @@
         <v>341</v>
       </c>
       <c r="F161" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G161" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H161" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I161" s="2" t="n">
-        <v>94.48</v>
+        <v>94.39</v>
       </c>
       <c r="J161" s="2" t="s">
         <v>16</v>
@@ -7710,10 +7710,10 @@
         <v>2018</v>
       </c>
       <c r="B162" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D162" s="2" t="s">
         <v>342</v>
@@ -7722,16 +7722,16 @@
         <v>343</v>
       </c>
       <c r="F162" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G162" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H162" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I162" s="2" t="n">
-        <v>94.39</v>
+        <v>94.31</v>
       </c>
       <c r="J162" s="2" t="s">
         <v>16</v>
@@ -7745,7 +7745,7 @@
         <v>5</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D163" s="2" t="s">
         <v>344</v>
@@ -7754,16 +7754,16 @@
         <v>345</v>
       </c>
       <c r="F163" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G163" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H163" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I163" s="2" t="n">
-        <v>94.31</v>
+        <v>94.21</v>
       </c>
       <c r="J163" s="2" t="s">
         <v>16</v>
@@ -7774,10 +7774,10 @@
         <v>2018</v>
       </c>
       <c r="B164" s="2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>110</v>
+        <v>52</v>
       </c>
       <c r="D164" s="2" t="s">
         <v>346</v>
@@ -7786,10 +7786,10 @@
         <v>347</v>
       </c>
       <c r="F164" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G164" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H164" s="2" t="s">
         <v>15</v>
@@ -7806,10 +7806,10 @@
         <v>2018</v>
       </c>
       <c r="B165" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>56</v>
+        <v>101</v>
       </c>
       <c r="D165" s="2" t="s">
         <v>348</v>
@@ -7818,16 +7818,16 @@
         <v>349</v>
       </c>
       <c r="F165" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G165" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H165" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I165" s="2" t="n">
-        <v>94.21</v>
+        <v>94.1</v>
       </c>
       <c r="J165" s="2" t="s">
         <v>16</v>
@@ -7841,7 +7841,7 @@
         <v>13</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D166" s="2" t="s">
         <v>350</v>
@@ -7850,16 +7850,16 @@
         <v>351</v>
       </c>
       <c r="F166" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G166" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H166" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I166" s="2" t="n">
-        <v>94.1</v>
+        <v>94.03</v>
       </c>
       <c r="J166" s="2" t="s">
         <v>16</v>
@@ -7870,10 +7870,10 @@
         <v>2018</v>
       </c>
       <c r="B167" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D167" s="2" t="s">
         <v>352</v>
@@ -7882,16 +7882,16 @@
         <v>353</v>
       </c>
       <c r="F167" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G167" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H167" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I167" s="2" t="n">
-        <v>94.03</v>
+        <v>93.88</v>
       </c>
       <c r="J167" s="2" t="s">
         <v>16</v>
@@ -7902,10 +7902,10 @@
         <v>2018</v>
       </c>
       <c r="B168" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="D168" s="2" t="s">
         <v>354</v>
@@ -7914,16 +7914,16 @@
         <v>355</v>
       </c>
       <c r="F168" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G168" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H168" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I168" s="2" t="n">
-        <v>93.88</v>
+        <v>93.62</v>
       </c>
       <c r="J168" s="2" t="s">
         <v>16</v>
@@ -7937,7 +7937,7 @@
         <v>13</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D169" s="2" t="s">
         <v>356</v>
@@ -7946,16 +7946,16 @@
         <v>357</v>
       </c>
       <c r="F169" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G169" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H169" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I169" s="2" t="n">
-        <v>93.62</v>
+        <v>93.53</v>
       </c>
       <c r="J169" s="2" t="s">
         <v>16</v>
@@ -7966,10 +7966,10 @@
         <v>2018</v>
       </c>
       <c r="B170" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>105</v>
+        <v>49</v>
       </c>
       <c r="D170" s="2" t="s">
         <v>358</v>
@@ -7978,16 +7978,16 @@
         <v>359</v>
       </c>
       <c r="F170" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G170" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H170" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I170" s="2" t="n">
-        <v>93.53</v>
+        <v>93.51</v>
       </c>
       <c r="J170" s="2" t="s">
         <v>16</v>
@@ -7998,10 +7998,10 @@
         <v>2018</v>
       </c>
       <c r="B171" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>53</v>
+        <v>101</v>
       </c>
       <c r="D171" s="2" t="s">
         <v>360</v>
@@ -8010,16 +8010,16 @@
         <v>361</v>
       </c>
       <c r="F171" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G171" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H171" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I171" s="2" t="n">
-        <v>93.51</v>
+        <v>93.42</v>
       </c>
       <c r="J171" s="2" t="s">
         <v>16</v>
@@ -8030,10 +8030,10 @@
         <v>2018</v>
       </c>
       <c r="B172" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D172" s="2" t="s">
         <v>362</v>
@@ -8042,16 +8042,16 @@
         <v>363</v>
       </c>
       <c r="F172" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G172" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H172" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I172" s="2" t="n">
-        <v>93.42</v>
+        <v>93.24</v>
       </c>
       <c r="J172" s="2" t="s">
         <v>16</v>
@@ -8062,10 +8062,10 @@
         <v>2018</v>
       </c>
       <c r="B173" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="D173" s="2" t="s">
         <v>364</v>
@@ -8074,10 +8074,10 @@
         <v>365</v>
       </c>
       <c r="F173" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G173" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H173" s="2" t="s">
         <v>15</v>
@@ -8097,7 +8097,7 @@
         <v>13</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D174" s="2" t="s">
         <v>366</v>
@@ -8106,10 +8106,10 @@
         <v>367</v>
       </c>
       <c r="F174" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G174" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H174" s="2" t="s">
         <v>15</v>
@@ -8126,10 +8126,10 @@
         <v>2018</v>
       </c>
       <c r="B175" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D175" s="2" t="s">
         <v>368</v>
@@ -8138,16 +8138,16 @@
         <v>369</v>
       </c>
       <c r="F175" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G175" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H175" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I175" s="2" t="n">
-        <v>93.24</v>
+        <v>93.21</v>
       </c>
       <c r="J175" s="2" t="s">
         <v>16</v>
@@ -8161,7 +8161,7 @@
         <v>5</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D176" s="2" t="s">
         <v>370</v>
@@ -8170,16 +8170,16 @@
         <v>371</v>
       </c>
       <c r="F176" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G176" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H176" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I176" s="2" t="n">
-        <v>93.21</v>
+        <v>93.13</v>
       </c>
       <c r="J176" s="2" t="s">
         <v>16</v>
@@ -8190,10 +8190,10 @@
         <v>2018</v>
       </c>
       <c r="B177" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="D177" s="2" t="s">
         <v>372</v>
@@ -8202,16 +8202,16 @@
         <v>373</v>
       </c>
       <c r="F177" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G177" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H177" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I177" s="2" t="n">
-        <v>93.13</v>
+        <v>93.06</v>
       </c>
       <c r="J177" s="2" t="s">
         <v>16</v>
@@ -8225,7 +8225,7 @@
         <v>13</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D178" s="2" t="s">
         <v>374</v>
@@ -8234,16 +8234,16 @@
         <v>375</v>
       </c>
       <c r="F178" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G178" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H178" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I178" s="2" t="n">
-        <v>93.06</v>
+        <v>92.78</v>
       </c>
       <c r="J178" s="2" t="s">
         <v>16</v>
@@ -8257,7 +8257,7 @@
         <v>13</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D179" s="2" t="s">
         <v>376</v>
@@ -8266,16 +8266,16 @@
         <v>377</v>
       </c>
       <c r="F179" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G179" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H179" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I179" s="2" t="n">
-        <v>92.78</v>
+        <v>92.62</v>
       </c>
       <c r="J179" s="2" t="s">
         <v>16</v>
@@ -8289,7 +8289,7 @@
         <v>13</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D180" s="2" t="s">
         <v>378</v>
@@ -8298,16 +8298,16 @@
         <v>379</v>
       </c>
       <c r="F180" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G180" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H180" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I180" s="2" t="n">
-        <v>92.62</v>
+        <v>92.42</v>
       </c>
       <c r="J180" s="2" t="s">
         <v>16</v>
@@ -8321,7 +8321,7 @@
         <v>13</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D181" s="2" t="s">
         <v>380</v>
@@ -8330,16 +8330,16 @@
         <v>381</v>
       </c>
       <c r="F181" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G181" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H181" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I181" s="2" t="n">
-        <v>92.42</v>
+        <v>92.37</v>
       </c>
       <c r="J181" s="2" t="s">
         <v>16</v>
@@ -8350,10 +8350,10 @@
         <v>2018</v>
       </c>
       <c r="B182" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D182" s="2" t="s">
         <v>382</v>
@@ -8362,16 +8362,16 @@
         <v>383</v>
       </c>
       <c r="F182" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G182" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H182" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I182" s="2" t="n">
-        <v>92.37</v>
+        <v>91.68</v>
       </c>
       <c r="J182" s="2" t="s">
         <v>16</v>
@@ -8382,10 +8382,10 @@
         <v>2018</v>
       </c>
       <c r="B183" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="D183" s="2" t="s">
         <v>384</v>
@@ -8394,16 +8394,16 @@
         <v>385</v>
       </c>
       <c r="F183" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G183" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H183" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I183" s="2" t="n">
-        <v>91.68</v>
+        <v>91.33</v>
       </c>
       <c r="J183" s="2" t="s">
         <v>16</v>
@@ -8417,7 +8417,7 @@
         <v>13</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D184" s="2" t="s">
         <v>386</v>
@@ -8426,16 +8426,16 @@
         <v>387</v>
       </c>
       <c r="F184" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G184" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H184" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I184" s="2" t="n">
-        <v>91.33</v>
+        <v>91.2</v>
       </c>
       <c r="J184" s="2" t="s">
         <v>16</v>
@@ -8449,7 +8449,7 @@
         <v>13</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D185" s="2" t="s">
         <v>388</v>
@@ -8458,16 +8458,16 @@
         <v>389</v>
       </c>
       <c r="F185" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G185" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H185" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I185" s="2" t="n">
-        <v>91.2</v>
+        <v>90.57</v>
       </c>
       <c r="J185" s="2" t="s">
         <v>16</v>
@@ -8481,7 +8481,7 @@
         <v>13</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D186" s="2" t="s">
         <v>390</v>
@@ -8490,16 +8490,16 @@
         <v>391</v>
       </c>
       <c r="F186" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G186" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H186" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I186" s="2" t="n">
-        <v>90.57</v>
+        <v>87.36</v>
       </c>
       <c r="J186" s="2" t="s">
         <v>16</v>
@@ -8513,7 +8513,7 @@
         <v>13</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D187" s="2" t="s">
         <v>392</v>
@@ -8522,16 +8522,16 @@
         <v>393</v>
       </c>
       <c r="F187" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G187" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H187" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I187" s="2" t="n">
-        <v>87.36</v>
+        <v>84.73</v>
       </c>
       <c r="J187" s="2" t="s">
         <v>16</v>
@@ -8542,28 +8542,28 @@
         <v>2018</v>
       </c>
       <c r="B188" s="2" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>105</v>
+        <v>394</v>
       </c>
       <c r="D188" s="2" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="E188" s="2" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="F188" s="2" t="s">
-        <v>51</v>
+        <v>397</v>
       </c>
       <c r="G188" s="2" t="s">
-        <v>52</v>
+        <v>398</v>
       </c>
       <c r="H188" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I188" s="2" t="n">
-        <v>84.73</v>
+        <v>97.97</v>
       </c>
       <c r="J188" s="2" t="s">
         <v>16</v>
@@ -8577,25 +8577,25 @@
         <v>4</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="D189" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="E189" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="F189" s="2" t="s">
         <v>397</v>
       </c>
-      <c r="E189" s="2" t="s">
+      <c r="G189" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="F189" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="G189" s="2" t="s">
-        <v>400</v>
-      </c>
       <c r="H189" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I189" s="2" t="n">
-        <v>97.97</v>
+        <v>97.44</v>
       </c>
       <c r="J189" s="2" t="s">
         <v>16</v>
@@ -8609,7 +8609,7 @@
         <v>4</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="D190" s="2" t="s">
         <v>401</v>
@@ -8618,16 +8618,16 @@
         <v>402</v>
       </c>
       <c r="F190" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G190" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H190" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I190" s="2" t="n">
-        <v>97.44</v>
+        <v>97.42</v>
       </c>
       <c r="J190" s="2" t="s">
         <v>16</v>
@@ -8638,28 +8638,28 @@
         <v>2018</v>
       </c>
       <c r="B191" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>396</v>
+        <v>403</v>
       </c>
       <c r="D191" s="2" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="E191" s="2" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="F191" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G191" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H191" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I191" s="2" t="n">
-        <v>97.42</v>
+        <v>97.31</v>
       </c>
       <c r="J191" s="2" t="s">
         <v>16</v>
@@ -8670,10 +8670,10 @@
         <v>2018</v>
       </c>
       <c r="B192" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>405</v>
+        <v>394</v>
       </c>
       <c r="D192" s="2" t="s">
         <v>406</v>
@@ -8682,16 +8682,16 @@
         <v>407</v>
       </c>
       <c r="F192" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G192" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H192" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I192" s="2" t="n">
-        <v>97.31</v>
+        <v>97</v>
       </c>
       <c r="J192" s="2" t="s">
         <v>16</v>
@@ -8705,7 +8705,7 @@
         <v>4</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="D193" s="2" t="s">
         <v>408</v>
@@ -8714,16 +8714,16 @@
         <v>409</v>
       </c>
       <c r="F193" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G193" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H193" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I193" s="2" t="n">
-        <v>97</v>
+        <v>96.97</v>
       </c>
       <c r="J193" s="2" t="s">
         <v>16</v>
@@ -8734,10 +8734,10 @@
         <v>2018</v>
       </c>
       <c r="B194" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>396</v>
+        <v>403</v>
       </c>
       <c r="D194" s="2" t="s">
         <v>410</v>
@@ -8746,16 +8746,16 @@
         <v>411</v>
       </c>
       <c r="F194" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G194" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H194" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I194" s="2" t="n">
-        <v>96.97</v>
+        <v>96.93</v>
       </c>
       <c r="J194" s="2" t="s">
         <v>16</v>
@@ -8766,10 +8766,10 @@
         <v>2018</v>
       </c>
       <c r="B195" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>405</v>
+        <v>394</v>
       </c>
       <c r="D195" s="2" t="s">
         <v>412</v>
@@ -8778,16 +8778,16 @@
         <v>413</v>
       </c>
       <c r="F195" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G195" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H195" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I195" s="2" t="n">
-        <v>96.93</v>
+        <v>96.79</v>
       </c>
       <c r="J195" s="2" t="s">
         <v>16</v>
@@ -8798,28 +8798,28 @@
         <v>2018</v>
       </c>
       <c r="B196" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>396</v>
+        <v>414</v>
       </c>
       <c r="D196" s="2" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E196" s="2" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="F196" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G196" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H196" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I196" s="2" t="n">
-        <v>96.79</v>
+        <v>96.77</v>
       </c>
       <c r="J196" s="2" t="s">
         <v>16</v>
@@ -8830,10 +8830,10 @@
         <v>2018</v>
       </c>
       <c r="B197" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>416</v>
+        <v>403</v>
       </c>
       <c r="D197" s="2" t="s">
         <v>417</v>
@@ -8842,16 +8842,16 @@
         <v>418</v>
       </c>
       <c r="F197" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G197" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H197" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I197" s="2" t="n">
-        <v>96.77</v>
+        <v>96.55</v>
       </c>
       <c r="J197" s="2" t="s">
         <v>16</v>
@@ -8862,10 +8862,10 @@
         <v>2018</v>
       </c>
       <c r="B198" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>405</v>
+        <v>394</v>
       </c>
       <c r="D198" s="2" t="s">
         <v>419</v>
@@ -8874,16 +8874,16 @@
         <v>420</v>
       </c>
       <c r="F198" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G198" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H198" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I198" s="2" t="n">
-        <v>96.55</v>
+        <v>96.46</v>
       </c>
       <c r="J198" s="2" t="s">
         <v>16</v>
@@ -8894,10 +8894,10 @@
         <v>2018</v>
       </c>
       <c r="B199" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>396</v>
+        <v>403</v>
       </c>
       <c r="D199" s="2" t="s">
         <v>421</v>
@@ -8906,16 +8906,16 @@
         <v>422</v>
       </c>
       <c r="F199" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G199" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H199" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I199" s="2" t="n">
-        <v>96.46</v>
+        <v>96.38</v>
       </c>
       <c r="J199" s="2" t="s">
         <v>16</v>
@@ -8929,7 +8929,7 @@
         <v>3</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="D200" s="2" t="s">
         <v>423</v>
@@ -8938,16 +8938,16 @@
         <v>424</v>
       </c>
       <c r="F200" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G200" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H200" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I200" s="2" t="n">
-        <v>96.38</v>
+        <v>96.37</v>
       </c>
       <c r="J200" s="2" t="s">
         <v>16</v>
@@ -8958,10 +8958,10 @@
         <v>2018</v>
       </c>
       <c r="B201" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>405</v>
+        <v>394</v>
       </c>
       <c r="D201" s="2" t="s">
         <v>425</v>
@@ -8970,16 +8970,16 @@
         <v>426</v>
       </c>
       <c r="F201" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G201" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H201" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I201" s="2" t="n">
-        <v>96.37</v>
+        <v>96.33</v>
       </c>
       <c r="J201" s="2" t="s">
         <v>16</v>
@@ -8993,7 +8993,7 @@
         <v>4</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="D202" s="2" t="s">
         <v>427</v>
@@ -9002,16 +9002,16 @@
         <v>428</v>
       </c>
       <c r="F202" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G202" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H202" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I202" s="2" t="n">
-        <v>96.33</v>
+        <v>96.23</v>
       </c>
       <c r="J202" s="2" t="s">
         <v>16</v>
@@ -9022,10 +9022,10 @@
         <v>2018</v>
       </c>
       <c r="B203" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>396</v>
+        <v>403</v>
       </c>
       <c r="D203" s="2" t="s">
         <v>429</v>
@@ -9034,16 +9034,16 @@
         <v>430</v>
       </c>
       <c r="F203" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G203" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H203" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I203" s="2" t="n">
-        <v>96.23</v>
+        <v>95.88</v>
       </c>
       <c r="J203" s="2" t="s">
         <v>16</v>
@@ -9057,7 +9057,7 @@
         <v>3</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="D204" s="2" t="s">
         <v>431</v>
@@ -9066,16 +9066,16 @@
         <v>432</v>
       </c>
       <c r="F204" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G204" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H204" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I204" s="2" t="n">
-        <v>95.88</v>
+        <v>95.84</v>
       </c>
       <c r="J204" s="2" t="s">
         <v>16</v>
@@ -9089,7 +9089,7 @@
         <v>3</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="D205" s="2" t="s">
         <v>433</v>
@@ -9098,16 +9098,16 @@
         <v>434</v>
       </c>
       <c r="F205" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G205" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H205" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I205" s="2" t="n">
-        <v>95.84</v>
+        <v>95.75</v>
       </c>
       <c r="J205" s="2" t="s">
         <v>16</v>
@@ -9118,10 +9118,10 @@
         <v>2018</v>
       </c>
       <c r="B206" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>405</v>
+        <v>394</v>
       </c>
       <c r="D206" s="2" t="s">
         <v>435</v>
@@ -9130,10 +9130,10 @@
         <v>436</v>
       </c>
       <c r="F206" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G206" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H206" s="2" t="s">
         <v>15</v>
@@ -9150,28 +9150,28 @@
         <v>2018</v>
       </c>
       <c r="B207" s="2" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>396</v>
+        <v>437</v>
       </c>
       <c r="D207" s="2" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="E207" s="2" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="F207" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G207" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H207" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I207" s="2" t="n">
-        <v>95.75</v>
+        <v>95.74</v>
       </c>
       <c r="J207" s="2" t="s">
         <v>16</v>
@@ -9182,10 +9182,10 @@
         <v>2018</v>
       </c>
       <c r="B208" s="2" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>439</v>
+        <v>394</v>
       </c>
       <c r="D208" s="2" t="s">
         <v>440</v>
@@ -9194,16 +9194,16 @@
         <v>441</v>
       </c>
       <c r="F208" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G208" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H208" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I208" s="2" t="n">
-        <v>95.74</v>
+        <v>95.65</v>
       </c>
       <c r="J208" s="2" t="s">
         <v>16</v>
@@ -9214,28 +9214,28 @@
         <v>2018</v>
       </c>
       <c r="B209" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>396</v>
+        <v>442</v>
       </c>
       <c r="D209" s="2" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E209" s="2" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="F209" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G209" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H209" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I209" s="2" t="n">
-        <v>95.65</v>
+        <v>95.57</v>
       </c>
       <c r="J209" s="2" t="s">
         <v>16</v>
@@ -9246,10 +9246,10 @@
         <v>2018</v>
       </c>
       <c r="B210" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>444</v>
+        <v>414</v>
       </c>
       <c r="D210" s="2" t="s">
         <v>445</v>
@@ -9258,16 +9258,16 @@
         <v>446</v>
       </c>
       <c r="F210" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G210" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H210" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I210" s="2" t="n">
-        <v>95.57</v>
+        <v>95.54</v>
       </c>
       <c r="J210" s="2" t="s">
         <v>16</v>
@@ -9278,28 +9278,28 @@
         <v>2018</v>
       </c>
       <c r="B211" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>416</v>
+        <v>394</v>
       </c>
       <c r="D211" s="2" t="s">
         <v>447</v>
       </c>
       <c r="E211" s="2" t="s">
-        <v>448</v>
+        <v>394</v>
       </c>
       <c r="F211" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G211" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H211" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I211" s="2" t="n">
-        <v>95.54</v>
+        <v>95.32</v>
       </c>
       <c r="J211" s="2" t="s">
         <v>16</v>
@@ -9310,28 +9310,28 @@
         <v>2018</v>
       </c>
       <c r="B212" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>396</v>
+        <v>414</v>
       </c>
       <c r="D212" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="E212" s="2" t="s">
         <v>449</v>
       </c>
-      <c r="E212" s="2" t="s">
-        <v>396</v>
-      </c>
       <c r="F212" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G212" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H212" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I212" s="2" t="n">
-        <v>95.32</v>
+        <v>95.29</v>
       </c>
       <c r="J212" s="2" t="s">
         <v>16</v>
@@ -9342,10 +9342,10 @@
         <v>2018</v>
       </c>
       <c r="B213" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>416</v>
+        <v>394</v>
       </c>
       <c r="D213" s="2" t="s">
         <v>450</v>
@@ -9354,16 +9354,16 @@
         <v>451</v>
       </c>
       <c r="F213" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G213" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H213" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I213" s="2" t="n">
-        <v>95.29</v>
+        <v>95.26</v>
       </c>
       <c r="J213" s="2" t="s">
         <v>16</v>
@@ -9377,7 +9377,7 @@
         <v>4</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="D214" s="2" t="s">
         <v>452</v>
@@ -9386,16 +9386,16 @@
         <v>453</v>
       </c>
       <c r="F214" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G214" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H214" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I214" s="2" t="n">
-        <v>95.26</v>
+        <v>94.8</v>
       </c>
       <c r="J214" s="2" t="s">
         <v>16</v>
@@ -9406,10 +9406,10 @@
         <v>2018</v>
       </c>
       <c r="B215" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>396</v>
+        <v>442</v>
       </c>
       <c r="D215" s="2" t="s">
         <v>454</v>
@@ -9418,16 +9418,16 @@
         <v>455</v>
       </c>
       <c r="F215" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G215" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H215" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I215" s="2" t="n">
-        <v>94.8</v>
+        <v>94.67</v>
       </c>
       <c r="J215" s="2" t="s">
         <v>16</v>
@@ -9438,10 +9438,10 @@
         <v>2018</v>
       </c>
       <c r="B216" s="2" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>444</v>
+        <v>437</v>
       </c>
       <c r="D216" s="2" t="s">
         <v>456</v>
@@ -9450,16 +9450,16 @@
         <v>457</v>
       </c>
       <c r="F216" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G216" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H216" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I216" s="2" t="n">
-        <v>94.67</v>
+        <v>94.57</v>
       </c>
       <c r="J216" s="2" t="s">
         <v>16</v>
@@ -9470,10 +9470,10 @@
         <v>2018</v>
       </c>
       <c r="B217" s="2" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>439</v>
+        <v>403</v>
       </c>
       <c r="D217" s="2" t="s">
         <v>458</v>
@@ -9482,16 +9482,16 @@
         <v>459</v>
       </c>
       <c r="F217" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G217" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H217" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I217" s="2" t="n">
-        <v>94.57</v>
+        <v>94.56</v>
       </c>
       <c r="J217" s="2" t="s">
         <v>16</v>
@@ -9502,10 +9502,10 @@
         <v>2018</v>
       </c>
       <c r="B218" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>405</v>
+        <v>442</v>
       </c>
       <c r="D218" s="2" t="s">
         <v>460</v>
@@ -9514,16 +9514,16 @@
         <v>461</v>
       </c>
       <c r="F218" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G218" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H218" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I218" s="2" t="n">
-        <v>94.56</v>
+        <v>94.39</v>
       </c>
       <c r="J218" s="2" t="s">
         <v>16</v>
@@ -9534,10 +9534,10 @@
         <v>2018</v>
       </c>
       <c r="B219" s="2" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>444</v>
+        <v>437</v>
       </c>
       <c r="D219" s="2" t="s">
         <v>462</v>
@@ -9546,16 +9546,16 @@
         <v>463</v>
       </c>
       <c r="F219" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G219" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H219" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I219" s="2" t="n">
-        <v>94.39</v>
+        <v>94.2</v>
       </c>
       <c r="J219" s="2" t="s">
         <v>16</v>
@@ -9569,7 +9569,7 @@
         <v>15</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="D220" s="2" t="s">
         <v>464</v>
@@ -9578,16 +9578,16 @@
         <v>465</v>
       </c>
       <c r="F220" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G220" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H220" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I220" s="2" t="n">
-        <v>94.2</v>
+        <v>93.59</v>
       </c>
       <c r="J220" s="2" t="s">
         <v>16</v>
@@ -9598,10 +9598,10 @@
         <v>2018</v>
       </c>
       <c r="B221" s="2" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C221" s="2" t="s">
-        <v>439</v>
+        <v>414</v>
       </c>
       <c r="D221" s="2" t="s">
         <v>466</v>
@@ -9610,16 +9610,16 @@
         <v>467</v>
       </c>
       <c r="F221" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G221" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H221" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I221" s="2" t="n">
-        <v>93.59</v>
+        <v>93.54</v>
       </c>
       <c r="J221" s="2" t="s">
         <v>16</v>
@@ -9630,10 +9630,10 @@
         <v>2018</v>
       </c>
       <c r="B222" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C222" s="2" t="s">
-        <v>416</v>
+        <v>442</v>
       </c>
       <c r="D222" s="2" t="s">
         <v>468</v>
@@ -9642,16 +9642,16 @@
         <v>469</v>
       </c>
       <c r="F222" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G222" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H222" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I222" s="2" t="n">
-        <v>93.54</v>
+        <v>93.12</v>
       </c>
       <c r="J222" s="2" t="s">
         <v>16</v>
@@ -9662,28 +9662,28 @@
         <v>2018</v>
       </c>
       <c r="B223" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C223" s="2" t="s">
-        <v>444</v>
+        <v>414</v>
       </c>
       <c r="D223" s="2" t="s">
         <v>470</v>
       </c>
       <c r="E223" s="2" t="s">
-        <v>471</v>
+        <v>414</v>
       </c>
       <c r="F223" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G223" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H223" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I223" s="2" t="n">
-        <v>93.12</v>
+        <v>92.93</v>
       </c>
       <c r="J223" s="2" t="s">
         <v>16</v>
@@ -9697,25 +9697,25 @@
         <v>2</v>
       </c>
       <c r="C224" s="2" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="D224" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="E224" s="2" t="s">
         <v>472</v>
       </c>
-      <c r="E224" s="2" t="s">
-        <v>416</v>
-      </c>
       <c r="F224" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G224" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H224" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I224" s="2" t="n">
-        <v>92.93</v>
+        <v>92.74</v>
       </c>
       <c r="J224" s="2" t="s">
         <v>16</v>
@@ -9726,10 +9726,10 @@
         <v>2018</v>
       </c>
       <c r="B225" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C225" s="2" t="s">
-        <v>416</v>
+        <v>394</v>
       </c>
       <c r="D225" s="2" t="s">
         <v>473</v>
@@ -9738,10 +9738,10 @@
         <v>474</v>
       </c>
       <c r="F225" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G225" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H225" s="2" t="s">
         <v>15</v>
@@ -9761,7 +9761,7 @@
         <v>2</v>
       </c>
       <c r="C226" s="2" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="D226" s="2" t="s">
         <v>475</v>
@@ -9770,10 +9770,10 @@
         <v>476</v>
       </c>
       <c r="F226" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G226" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H226" s="2" t="s">
         <v>15</v>
@@ -9793,7 +9793,7 @@
         <v>1</v>
       </c>
       <c r="C227" s="2" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="D227" s="2" t="s">
         <v>477</v>
@@ -9802,10 +9802,10 @@
         <v>478</v>
       </c>
       <c r="F227" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G227" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H227" s="2" t="s">
         <v>15</v>
@@ -9825,7 +9825,7 @@
         <v>1</v>
       </c>
       <c r="C228" s="2" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="D228" s="2" t="s">
         <v>479</v>
@@ -9834,10 +9834,10 @@
         <v>480</v>
       </c>
       <c r="F228" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G228" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H228" s="2" t="s">
         <v>15</v>
@@ -9857,7 +9857,7 @@
         <v>2</v>
       </c>
       <c r="C229" s="2" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="D229" s="2" t="s">
         <v>481</v>
@@ -9866,10 +9866,10 @@
         <v>482</v>
       </c>
       <c r="F229" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G229" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H229" s="2" t="s">
         <v>15</v>

--- a/output/graficos_nacionales/plot_nacional_e_basneta_a_2018.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_basneta_a_2018.xlsx
@@ -2131,7 +2131,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 20:03</t>
+    <t xml:space="preserve">2026-09-18 11:26</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_e_basneta_a_2018.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_basneta_a_2018.xlsx
@@ -2131,7 +2131,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 11:26</t>
+    <t xml:space="preserve">2026-09-24 00:18</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
